--- a/data/nzd0019/nzd0019.xlsx
+++ b/data/nzd0019/nzd0019.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N434"/>
+  <dimension ref="A1:N438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21258,6 +21258,198 @@
         <v>410.14</v>
       </c>
       <c r="N434" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>401.03</v>
+      </c>
+      <c r="C435" t="n">
+        <v>398.85</v>
+      </c>
+      <c r="D435" t="n">
+        <v>398.86</v>
+      </c>
+      <c r="E435" t="n">
+        <v>405.33</v>
+      </c>
+      <c r="F435" t="n">
+        <v>425.09</v>
+      </c>
+      <c r="G435" t="n">
+        <v>430.22</v>
+      </c>
+      <c r="H435" t="n">
+        <v>420.49</v>
+      </c>
+      <c r="I435" t="n">
+        <v>417.99</v>
+      </c>
+      <c r="J435" t="n">
+        <v>419.78</v>
+      </c>
+      <c r="K435" t="n">
+        <v>418.95</v>
+      </c>
+      <c r="L435" t="n">
+        <v>413.55</v>
+      </c>
+      <c r="M435" t="n">
+        <v>408.34</v>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>406.02</v>
+      </c>
+      <c r="C436" t="n">
+        <v>399.86</v>
+      </c>
+      <c r="D436" t="n">
+        <v>399.69</v>
+      </c>
+      <c r="E436" t="n">
+        <v>406.31</v>
+      </c>
+      <c r="F436" t="n">
+        <v>426.13</v>
+      </c>
+      <c r="G436" t="n">
+        <v>431.17</v>
+      </c>
+      <c r="H436" t="n">
+        <v>421.44</v>
+      </c>
+      <c r="I436" t="n">
+        <v>418.84</v>
+      </c>
+      <c r="J436" t="n">
+        <v>420.77</v>
+      </c>
+      <c r="K436" t="n">
+        <v>419.68</v>
+      </c>
+      <c r="L436" t="n">
+        <v>414.8</v>
+      </c>
+      <c r="M436" t="n">
+        <v>406.72</v>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>407.2</v>
+      </c>
+      <c r="C437" t="n">
+        <v>401.76</v>
+      </c>
+      <c r="D437" t="n">
+        <v>401.8</v>
+      </c>
+      <c r="E437" t="n">
+        <v>407.25</v>
+      </c>
+      <c r="F437" t="n">
+        <v>426.55</v>
+      </c>
+      <c r="G437" t="n">
+        <v>431.66</v>
+      </c>
+      <c r="H437" t="n">
+        <v>422.11</v>
+      </c>
+      <c r="I437" t="n">
+        <v>419.51</v>
+      </c>
+      <c r="J437" t="n">
+        <v>419.65</v>
+      </c>
+      <c r="K437" t="n">
+        <v>419.21</v>
+      </c>
+      <c r="L437" t="n">
+        <v>414.24</v>
+      </c>
+      <c r="M437" t="n">
+        <v>406.82</v>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>408.18</v>
+      </c>
+      <c r="C438" t="n">
+        <v>403.73</v>
+      </c>
+      <c r="D438" t="n">
+        <v>401.57</v>
+      </c>
+      <c r="E438" t="n">
+        <v>407.41</v>
+      </c>
+      <c r="F438" t="n">
+        <v>426.33</v>
+      </c>
+      <c r="G438" t="n">
+        <v>434.53</v>
+      </c>
+      <c r="H438" t="n">
+        <v>422.03</v>
+      </c>
+      <c r="I438" t="n">
+        <v>419.12</v>
+      </c>
+      <c r="J438" t="n">
+        <v>419.71</v>
+      </c>
+      <c r="K438" t="n">
+        <v>419.24</v>
+      </c>
+      <c r="L438" t="n">
+        <v>413.96</v>
+      </c>
+      <c r="M438" t="n">
+        <v>406.41</v>
+      </c>
+      <c r="N438" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21274,7 +21466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B509"/>
+  <dimension ref="A1:B513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26367,6 +26559,46 @@
       </c>
       <c r="B509" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -26535,28 +26767,28 @@
         <v>0.0679</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03570626150073358</v>
+        <v>-0.03433224261339193</v>
       </c>
       <c r="J2" t="n">
+        <v>437</v>
+      </c>
+      <c r="K2" t="n">
         <v>433</v>
       </c>
-      <c r="K2" t="n">
-        <v>429</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.003156690085368119</v>
+        <v>0.002975217487395931</v>
       </c>
       <c r="M2" t="n">
-        <v>3.835796925328205</v>
+        <v>3.823051020746389</v>
       </c>
       <c r="N2" t="n">
-        <v>23.7737252155138</v>
+        <v>23.62896036945207</v>
       </c>
       <c r="O2" t="n">
-        <v>4.875830720555606</v>
+        <v>4.860962905582809</v>
       </c>
       <c r="P2" t="n">
-        <v>405.8253709071818</v>
+        <v>405.8116262055837</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26613,28 +26845,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01384829833743078</v>
+        <v>0.01128231604675778</v>
       </c>
       <c r="J3" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K3" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003786897024080638</v>
+        <v>0.0002565971637052966</v>
       </c>
       <c r="M3" t="n">
-        <v>4.255464267576775</v>
+        <v>4.237055942831265</v>
       </c>
       <c r="N3" t="n">
-        <v>30.23814013595671</v>
+        <v>30.01053521239214</v>
       </c>
       <c r="O3" t="n">
-        <v>5.498921724843581</v>
+        <v>5.478187219545544</v>
       </c>
       <c r="P3" t="n">
-        <v>402.0914852917833</v>
+        <v>402.1167528625144</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26691,28 +26923,28 @@
         <v>0.1523</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02711207082137128</v>
+        <v>0.01915560835324743</v>
       </c>
       <c r="J4" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K4" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001080040576597496</v>
+        <v>0.000549005921103074</v>
       </c>
       <c r="M4" t="n">
-        <v>4.990917969037262</v>
+        <v>4.986613514646107</v>
       </c>
       <c r="N4" t="n">
-        <v>40.60936908595389</v>
+        <v>40.42191615413007</v>
       </c>
       <c r="O4" t="n">
-        <v>6.372548084240235</v>
+        <v>6.357823224510891</v>
       </c>
       <c r="P4" t="n">
-        <v>404.1390417424596</v>
+        <v>404.2174757034447</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26769,28 +27001,28 @@
         <v>0.1123</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0008641795482966277</v>
+        <v>-0.005066309624153597</v>
       </c>
       <c r="J5" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K5" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L5" t="n">
-        <v>1.066955359951827e-06</v>
+        <v>3.740051219769391e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.958743931143915</v>
+        <v>4.943264521252884</v>
       </c>
       <c r="N5" t="n">
-        <v>41.80916537783624</v>
+        <v>41.52696440469713</v>
       </c>
       <c r="O5" t="n">
-        <v>6.466000725165149</v>
+        <v>6.444141867207543</v>
       </c>
       <c r="P5" t="n">
-        <v>409.8215967628538</v>
+        <v>409.8800596421069</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26847,28 +27079,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04251011062058684</v>
+        <v>0.03761746523531327</v>
       </c>
       <c r="J6" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K6" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002831025167936763</v>
+        <v>0.002263815242806833</v>
       </c>
       <c r="M6" t="n">
-        <v>4.840519790593417</v>
+        <v>4.820727081096272</v>
       </c>
       <c r="N6" t="n">
-        <v>38.0206677928691</v>
+        <v>37.73934189770496</v>
       </c>
       <c r="O6" t="n">
-        <v>6.166090154455179</v>
+        <v>6.143235458429455</v>
       </c>
       <c r="P6" t="n">
-        <v>427.5800684958705</v>
+        <v>427.6283040714729</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26925,28 +27157,28 @@
         <v>0.0931</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01031207210863275</v>
+        <v>-0.0126062419705133</v>
       </c>
       <c r="J7" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K7" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001426947194714812</v>
+        <v>0.0002178282020526279</v>
       </c>
       <c r="M7" t="n">
-        <v>5.260653440121722</v>
+        <v>5.230834085530379</v>
       </c>
       <c r="N7" t="n">
-        <v>44.50740231881899</v>
+        <v>44.13702756653836</v>
       </c>
       <c r="O7" t="n">
-        <v>6.671386836244694</v>
+        <v>6.643570392984359</v>
       </c>
       <c r="P7" t="n">
-        <v>433.4384398953596</v>
+        <v>433.461033284614</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27003,28 +27235,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03001688285889035</v>
+        <v>0.02911156996384655</v>
       </c>
       <c r="J8" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K8" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001291806439299159</v>
+        <v>0.001242191309818619</v>
       </c>
       <c r="M8" t="n">
-        <v>5.09566473181689</v>
+        <v>5.053942030590777</v>
       </c>
       <c r="N8" t="n">
-        <v>41.60855095968797</v>
+        <v>41.23286180642361</v>
       </c>
       <c r="O8" t="n">
-        <v>6.450469049587632</v>
+        <v>6.421281944162209</v>
       </c>
       <c r="P8" t="n">
-        <v>421.2074579172277</v>
+        <v>421.2163740118123</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27081,28 +27313,28 @@
         <v>0.1391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04215458197885068</v>
+        <v>0.04105093856619277</v>
       </c>
       <c r="J9" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K9" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003003664358755875</v>
+        <v>0.002912119265186197</v>
       </c>
       <c r="M9" t="n">
-        <v>4.731353993182756</v>
+        <v>4.693781254995727</v>
       </c>
       <c r="N9" t="n">
-        <v>35.15375548784419</v>
+        <v>34.83810867459367</v>
       </c>
       <c r="O9" t="n">
-        <v>5.929060253349108</v>
+        <v>5.90238161038353</v>
       </c>
       <c r="P9" t="n">
-        <v>418.3432525479832</v>
+        <v>418.3541369327218</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27159,28 +27391,28 @@
         <v>0.1166</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05572676315168616</v>
+        <v>0.05573072022569924</v>
       </c>
       <c r="J10" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K10" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005078385187661572</v>
+        <v>0.005192205539452321</v>
       </c>
       <c r="M10" t="n">
-        <v>4.870080604825294</v>
+        <v>4.829119755427625</v>
       </c>
       <c r="N10" t="n">
-        <v>36.26025523200092</v>
+        <v>35.93028994010158</v>
       </c>
       <c r="O10" t="n">
-        <v>6.021648879833572</v>
+        <v>5.994188013409454</v>
       </c>
       <c r="P10" t="n">
-        <v>418.4792328818954</v>
+        <v>418.4791964469417</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27237,28 +27469,28 @@
         <v>0.1266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1594273928678762</v>
+        <v>0.1610587452189615</v>
       </c>
       <c r="J11" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K11" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03823959611988481</v>
+        <v>0.03982780586645207</v>
       </c>
       <c r="M11" t="n">
-        <v>4.935174917563787</v>
+        <v>4.898252331624785</v>
       </c>
       <c r="N11" t="n">
-        <v>38.09951763718086</v>
+        <v>37.75856434919085</v>
       </c>
       <c r="O11" t="n">
-        <v>6.172480671268308</v>
+        <v>6.144799781049896</v>
       </c>
       <c r="P11" t="n">
-        <v>414.086254424563</v>
+        <v>414.0701528396066</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27315,28 +27547,28 @@
         <v>0.0862</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1003211014610307</v>
+        <v>0.1029228216113508</v>
       </c>
       <c r="J12" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K12" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01422328629536129</v>
+        <v>0.01528305634711091</v>
       </c>
       <c r="M12" t="n">
-        <v>5.20038377295669</v>
+        <v>5.166158865864419</v>
       </c>
       <c r="N12" t="n">
-        <v>41.41199994910757</v>
+        <v>41.05207694435094</v>
       </c>
       <c r="O12" t="n">
-        <v>6.435215610149171</v>
+        <v>6.407189473111509</v>
       </c>
       <c r="P12" t="n">
-        <v>410.01160959018</v>
+        <v>409.9858359800284</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27393,28 +27625,28 @@
         <v>0.0755</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3165134069057362</v>
+        <v>0.315939430345968</v>
       </c>
       <c r="J13" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K13" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09857999035325149</v>
+        <v>0.1002371977608428</v>
       </c>
       <c r="M13" t="n">
-        <v>5.902213601189758</v>
+        <v>5.85552073814968</v>
       </c>
       <c r="N13" t="n">
-        <v>54.25704349636793</v>
+        <v>53.76533299526393</v>
       </c>
       <c r="O13" t="n">
-        <v>7.365938059498459</v>
+        <v>7.332484776340413</v>
       </c>
       <c r="P13" t="n">
-        <v>398.8738974095364</v>
+        <v>398.8796035245394</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27452,7 +27684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N434"/>
+  <dimension ref="A1:N438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58655,6 +58887,294 @@
         </is>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>-34.80140562305609,173.38883458180104</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>-34.8014683012259,173.38971110767756</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>-34.801457883977186,173.39057107475386</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-34.80129776328529,173.39144118588933</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>-34.80108397082688,173.39227432040582</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>-34.800886369288285,173.3929660956436</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>-34.800625333650494,173.39370951279798</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>-34.800290532286446,173.39448856674275</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>-34.79990068889039,173.39517105797987</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>-34.79946398838521,173.39577936308854</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>-34.798987754496714,173.39636281861164</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>-34.7984357284842,173.39688698793066</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>-34.80136069796433,173.38883768178238</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>-34.80145919515107,173.38971132079044</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>-34.801450423578565,173.39057034560165</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-34.801288970859176,173.39144010829133</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>-34.801074716581184,173.3922724772884</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>-34.80087847912731,173.3929620504603</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>-34.80061792232853,173.3937043039879</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>-34.80028401344509,173.39448367886476</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>-34.79989364826294,173.39516440377795</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>-34.799459387414316,173.39577365568198</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>-34.79898091325604,173.39635195835388</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>-34.79844388423685,173.39690168056572</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>-34.80135007439547,173.38883841484363</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>-34.80144206491123,173.3897117216958</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>-34.80143145798678,173.39056849197436</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-34.801280537307576,173.3914390746772</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-34.80107097928964,173.39227173295265</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>-34.80087440946527,173.39295996399767</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>-34.80061269539607,173.39370063040658</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>-34.80027887506412,173.39447982606737</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>-34.79990161341719,173.39517193176405</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>-34.799462349683274,173.39577733031354</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>-34.798983978131986,173.39635682374913</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>-34.798443380795376,173.39690077361286</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>-34.80134125143151,173.38883902365708</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>-34.80142430355723,173.3897121373712</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>-34.801433525326175,173.3905686940285</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-34.80127910180944,173.3914388987429</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-34.801072936918544,173.3922721228428</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>-34.80085057287256,173.39294774329204</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>-34.80061331950741,173.39370106904312</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>-34.800281866062015,173.39448206874042</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>-34.79990118671251,173.395171528479</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>-34.79946216060229,173.39577709576258</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>-34.79898551056988,173.3963592564469</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>-34.79844544490536,173.39690449211966</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0019/nzd0019.xlsx
+++ b/data/nzd0019/nzd0019.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N438"/>
+  <dimension ref="A1:N441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21452,6 +21452,150 @@
       <c r="N438" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>408.24</v>
+      </c>
+      <c r="C439" t="n">
+        <v>404.18</v>
+      </c>
+      <c r="D439" t="n">
+        <v>402.46</v>
+      </c>
+      <c r="E439" t="n">
+        <v>407.85</v>
+      </c>
+      <c r="F439" t="n">
+        <v>427.05</v>
+      </c>
+      <c r="G439" t="n">
+        <v>435.08</v>
+      </c>
+      <c r="H439" t="n">
+        <v>422.57</v>
+      </c>
+      <c r="I439" t="n">
+        <v>419.99</v>
+      </c>
+      <c r="J439" t="n">
+        <v>420.3</v>
+      </c>
+      <c r="K439" t="n">
+        <v>419.88</v>
+      </c>
+      <c r="L439" t="n">
+        <v>414.64</v>
+      </c>
+      <c r="M439" t="n">
+        <v>407.34</v>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>408.91</v>
+      </c>
+      <c r="C440" t="n">
+        <v>403.94</v>
+      </c>
+      <c r="D440" t="n">
+        <v>403.49</v>
+      </c>
+      <c r="E440" t="n">
+        <v>408.31</v>
+      </c>
+      <c r="F440" t="n">
+        <v>427.36</v>
+      </c>
+      <c r="G440" t="n">
+        <v>435.4</v>
+      </c>
+      <c r="H440" t="n">
+        <v>423.18</v>
+      </c>
+      <c r="I440" t="n">
+        <v>420.4</v>
+      </c>
+      <c r="J440" t="n">
+        <v>420.88</v>
+      </c>
+      <c r="K440" t="n">
+        <v>420.27</v>
+      </c>
+      <c r="L440" t="n">
+        <v>415.58</v>
+      </c>
+      <c r="M440" t="n">
+        <v>407.75</v>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>408.81</v>
+      </c>
+      <c r="C441" t="n">
+        <v>403.8</v>
+      </c>
+      <c r="D441" t="n">
+        <v>403.28</v>
+      </c>
+      <c r="E441" t="n">
+        <v>408.06</v>
+      </c>
+      <c r="F441" t="n">
+        <v>427.25</v>
+      </c>
+      <c r="G441" t="n">
+        <v>435.37</v>
+      </c>
+      <c r="H441" t="n">
+        <v>422.76</v>
+      </c>
+      <c r="I441" t="n">
+        <v>420.83</v>
+      </c>
+      <c r="J441" t="n">
+        <v>420.85</v>
+      </c>
+      <c r="K441" t="n">
+        <v>420.43</v>
+      </c>
+      <c r="L441" t="n">
+        <v>415.22</v>
+      </c>
+      <c r="M441" t="n">
+        <v>407.84</v>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21466,7 +21610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B513"/>
+  <dimension ref="A1:B517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26599,6 +26743,46 @@
       </c>
       <c r="B513" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -26767,28 +26951,28 @@
         <v>0.0679</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03433224261339193</v>
+        <v>-0.02922160849001036</v>
       </c>
       <c r="J2" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K2" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002975217487395931</v>
+        <v>0.002183718769221965</v>
       </c>
       <c r="M2" t="n">
-        <v>3.823051020746389</v>
+        <v>3.815647990233173</v>
       </c>
       <c r="N2" t="n">
-        <v>23.62896036945207</v>
+        <v>23.56257745511764</v>
       </c>
       <c r="O2" t="n">
-        <v>4.860962905582809</v>
+        <v>4.854129938013366</v>
       </c>
       <c r="P2" t="n">
-        <v>405.8116262055837</v>
+        <v>405.7604839115779</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26845,28 +27029,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01128231604675778</v>
+        <v>0.01336557083847613</v>
       </c>
       <c r="J3" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K3" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002565971637052966</v>
+        <v>0.0003657841855947419</v>
       </c>
       <c r="M3" t="n">
-        <v>4.237055942831265</v>
+        <v>4.216985076003029</v>
       </c>
       <c r="N3" t="n">
-        <v>30.01053521239214</v>
+        <v>29.8217564500858</v>
       </c>
       <c r="O3" t="n">
-        <v>5.478187219545544</v>
+        <v>5.460929998643619</v>
       </c>
       <c r="P3" t="n">
-        <v>402.1167528625144</v>
+        <v>402.0961337281189</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26923,28 +27107,28 @@
         <v>0.1523</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01915560835324743</v>
+        <v>0.01693102841508643</v>
       </c>
       <c r="J4" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K4" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000549005921103074</v>
+        <v>0.0004357797539160657</v>
       </c>
       <c r="M4" t="n">
-        <v>4.986613514646107</v>
+        <v>4.963961685278144</v>
       </c>
       <c r="N4" t="n">
-        <v>40.42191615413007</v>
+        <v>40.16542226469626</v>
       </c>
       <c r="O4" t="n">
-        <v>6.357823224510891</v>
+        <v>6.337619605553512</v>
       </c>
       <c r="P4" t="n">
-        <v>404.2174757034447</v>
+        <v>404.2394932724009</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27001,28 +27185,28 @@
         <v>0.1123</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.005066309624153597</v>
+        <v>-0.007303413452335569</v>
       </c>
       <c r="J5" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K5" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L5" t="n">
-        <v>3.740051219769391e-05</v>
+        <v>7.896033439391825e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.943264521252884</v>
+        <v>4.920757510267918</v>
       </c>
       <c r="N5" t="n">
-        <v>41.52696440469713</v>
+        <v>41.26202227645826</v>
       </c>
       <c r="O5" t="n">
-        <v>6.444141867207543</v>
+        <v>6.423552154101207</v>
       </c>
       <c r="P5" t="n">
-        <v>409.8800596421069</v>
+        <v>409.9022030640953</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27079,28 +27263,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03761746523531327</v>
+        <v>0.03571505067121296</v>
       </c>
       <c r="J6" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K6" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002263815242806833</v>
+        <v>0.002073812645198569</v>
       </c>
       <c r="M6" t="n">
-        <v>4.820727081096272</v>
+        <v>4.797384427707873</v>
       </c>
       <c r="N6" t="n">
-        <v>37.73934189770496</v>
+        <v>37.49500791717252</v>
       </c>
       <c r="O6" t="n">
-        <v>6.143235458429455</v>
+        <v>6.123316741535793</v>
       </c>
       <c r="P6" t="n">
-        <v>427.6283040714729</v>
+        <v>427.647134343675</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27157,28 +27341,28 @@
         <v>0.0931</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0126062419705133</v>
+        <v>-0.009707718526889154</v>
       </c>
       <c r="J7" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K7" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002178282020526279</v>
+        <v>0.0001312150631930242</v>
       </c>
       <c r="M7" t="n">
-        <v>5.230834085530379</v>
+        <v>5.20883748420021</v>
       </c>
       <c r="N7" t="n">
-        <v>44.13702756653836</v>
+        <v>43.86677173289453</v>
       </c>
       <c r="O7" t="n">
-        <v>6.643570392984359</v>
+        <v>6.623199508764214</v>
       </c>
       <c r="P7" t="n">
-        <v>433.461033284614</v>
+        <v>433.4323421697147</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27235,28 +27419,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02911156996384655</v>
+        <v>0.03023477418126147</v>
       </c>
       <c r="J8" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K8" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001242191309818619</v>
+        <v>0.001361582295180352</v>
       </c>
       <c r="M8" t="n">
-        <v>5.053942030590777</v>
+        <v>5.025029888269049</v>
       </c>
       <c r="N8" t="n">
-        <v>41.23286180642361</v>
+        <v>40.95621739815347</v>
       </c>
       <c r="O8" t="n">
-        <v>6.421281944162209</v>
+        <v>6.399704477407802</v>
       </c>
       <c r="P8" t="n">
-        <v>421.2163740118123</v>
+        <v>421.2052567009939</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27313,28 +27497,28 @@
         <v>0.1391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04105093856619277</v>
+        <v>0.04231565883961118</v>
       </c>
       <c r="J9" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K9" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002912119265186197</v>
+        <v>0.003143858312535275</v>
       </c>
       <c r="M9" t="n">
-        <v>4.693781254995727</v>
+        <v>4.668055007026168</v>
       </c>
       <c r="N9" t="n">
-        <v>34.83810867459367</v>
+        <v>34.60729771107066</v>
       </c>
       <c r="O9" t="n">
-        <v>5.90238161038353</v>
+        <v>5.882796759286407</v>
       </c>
       <c r="P9" t="n">
-        <v>418.3541369327218</v>
+        <v>418.3416035354744</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27391,28 +27575,28 @@
         <v>0.1166</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05573072022569924</v>
+        <v>0.05666262312595371</v>
       </c>
       <c r="J10" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K10" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005192205539452321</v>
+        <v>0.00545355707412809</v>
       </c>
       <c r="M10" t="n">
-        <v>4.829119755427625</v>
+        <v>4.800984256176712</v>
       </c>
       <c r="N10" t="n">
-        <v>35.93028994010158</v>
+        <v>35.68901060762892</v>
       </c>
       <c r="O10" t="n">
-        <v>5.994188013409454</v>
+        <v>5.974028005259845</v>
       </c>
       <c r="P10" t="n">
-        <v>418.4791964469417</v>
+        <v>418.4699623404398</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27469,28 +27653,28 @@
         <v>0.1266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1610587452189615</v>
+        <v>0.1634397678906257</v>
       </c>
       <c r="J11" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K11" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03982780586645207</v>
+        <v>0.04158838119421759</v>
       </c>
       <c r="M11" t="n">
-        <v>4.898252331624785</v>
+        <v>4.876817992771318</v>
       </c>
       <c r="N11" t="n">
-        <v>37.75856434919085</v>
+        <v>37.52247515270691</v>
       </c>
       <c r="O11" t="n">
-        <v>6.144799781049896</v>
+        <v>6.125559170615113</v>
       </c>
       <c r="P11" t="n">
-        <v>414.0701528396066</v>
+        <v>414.0465615203831</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27547,28 +27731,28 @@
         <v>0.0862</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1029228216113508</v>
+        <v>0.1061344893586222</v>
       </c>
       <c r="J12" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K12" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01528305634711091</v>
+        <v>0.01648339418701172</v>
       </c>
       <c r="M12" t="n">
-        <v>5.166158865864419</v>
+        <v>5.147263732190784</v>
       </c>
       <c r="N12" t="n">
-        <v>41.05207694435094</v>
+        <v>40.81058808011643</v>
       </c>
       <c r="O12" t="n">
-        <v>6.407189473111509</v>
+        <v>6.388316529424355</v>
       </c>
       <c r="P12" t="n">
-        <v>409.9858359800284</v>
+        <v>409.9538997632672</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27625,28 +27809,28 @@
         <v>0.0755</v>
       </c>
       <c r="I13" t="n">
-        <v>0.315939430345968</v>
+        <v>0.3162660623905436</v>
       </c>
       <c r="J13" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K13" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1002371977608428</v>
+        <v>0.1019096720925724</v>
       </c>
       <c r="M13" t="n">
-        <v>5.85552073814968</v>
+        <v>5.817311852204959</v>
       </c>
       <c r="N13" t="n">
-        <v>53.76533299526393</v>
+        <v>53.39862042603253</v>
       </c>
       <c r="O13" t="n">
-        <v>7.332484776340413</v>
+        <v>7.307435967973482</v>
       </c>
       <c r="P13" t="n">
-        <v>398.8796035245394</v>
+        <v>398.8763492225947</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27684,7 +27868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N438"/>
+  <dimension ref="A1:N441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59175,6 +59359,222 @@
         </is>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>-34.80134071125003,173.3888390609314</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>-34.80142024639515,173.3897122323224</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>-34.80142552562155,173.39056791216694</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-34.801275154189526,173.3914384149236</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>-34.80106653013305,173.39227084683873</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>-34.80084600488426,173.39294540134577</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>-34.8006091067558,173.39369810824655</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>-34.80027519383587,173.3944770658546</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>-34.7998969907831,173.39516756284337</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>-34.79945812687432,173.39577209200908</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>-34.798981788934896,173.39635334846676</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>-34.79844076289961,173.39689605745815</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>-34.80133467922363,173.3888394771609</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>-34.80142241021494,173.38971218168177</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>-34.80141626753642,173.39056700731618</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-34.80127102713236,173.3914379091126</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>-34.80106377165593,173.39227029744814</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>-34.80084334714557,173.392944038759</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>-34.80060434790666,173.39369476364337</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>-34.80027204945335,173.39447470817305</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>-34.799892865970975,173.39516366442226</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>-34.799455668821224,173.39576904284704</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>-34.79897664432136,173.39634518155395</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>-34.79843869878936,173.39689233895174</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>-34.80133557952609,173.3888394150371</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>-34.801423672443136,173.38971215214139</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>-34.80141815510716,173.3905671918003</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-34.80127327009822,173.3914381840099</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-34.80106475047038,173.39227049239318</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-34.80084359630857,173.3929441665015</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-34.80060762449132,173.3936970664849</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>-34.80026875168627,173.39447223548285</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>-34.79989307932333,173.3951638660647</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>-34.799454660389166,173.3957677919088</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>-34.798978614598944,173.39634830930765</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>-34.79843824569199,173.39689152269426</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0019/nzd0019.xlsx
+++ b/data/nzd0019/nzd0019.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N441"/>
+  <dimension ref="A1:N443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21596,6 +21596,102 @@
       <c r="N441" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>408.55</v>
+      </c>
+      <c r="C442" t="n">
+        <v>403.18</v>
+      </c>
+      <c r="D442" t="n">
+        <v>402.52</v>
+      </c>
+      <c r="E442" t="n">
+        <v>406.48</v>
+      </c>
+      <c r="F442" t="n">
+        <v>425.92</v>
+      </c>
+      <c r="G442" t="n">
+        <v>434.48</v>
+      </c>
+      <c r="H442" t="n">
+        <v>421.4</v>
+      </c>
+      <c r="I442" t="n">
+        <v>420.25</v>
+      </c>
+      <c r="J442" t="n">
+        <v>419.76</v>
+      </c>
+      <c r="K442" t="n">
+        <v>419.41</v>
+      </c>
+      <c r="L442" t="n">
+        <v>414.24</v>
+      </c>
+      <c r="M442" t="n">
+        <v>407.29</v>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>408.63</v>
+      </c>
+      <c r="C443" t="n">
+        <v>403.7</v>
+      </c>
+      <c r="D443" t="n">
+        <v>403.03</v>
+      </c>
+      <c r="E443" t="n">
+        <v>406.55</v>
+      </c>
+      <c r="F443" t="n">
+        <v>426.49</v>
+      </c>
+      <c r="G443" t="n">
+        <v>434.11</v>
+      </c>
+      <c r="H443" t="n">
+        <v>421.42</v>
+      </c>
+      <c r="I443" t="n">
+        <v>420.54</v>
+      </c>
+      <c r="J443" t="n">
+        <v>420.41</v>
+      </c>
+      <c r="K443" t="n">
+        <v>419.46</v>
+      </c>
+      <c r="L443" t="n">
+        <v>414.93</v>
+      </c>
+      <c r="M443" t="n">
+        <v>407.56</v>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21610,7 +21706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B517"/>
+  <dimension ref="A1:B520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26783,6 +26879,36 @@
       </c>
       <c r="B517" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -26951,28 +27077,28 @@
         <v>0.0679</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02922160849001036</v>
+        <v>-0.02597283938003603</v>
       </c>
       <c r="J2" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K2" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002183718769221965</v>
+        <v>0.001740334572147284</v>
       </c>
       <c r="M2" t="n">
-        <v>3.815647990233173</v>
+        <v>3.810208127111875</v>
       </c>
       <c r="N2" t="n">
-        <v>23.56257745511764</v>
+        <v>23.51390814214882</v>
       </c>
       <c r="O2" t="n">
-        <v>4.854129938013366</v>
+        <v>4.849114160560548</v>
       </c>
       <c r="P2" t="n">
-        <v>405.7604839115779</v>
+        <v>405.7278295217495</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27029,28 +27155,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01336557083847613</v>
+        <v>0.01423567886551267</v>
       </c>
       <c r="J3" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K3" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003657841855947419</v>
+        <v>0.0004193728433040667</v>
       </c>
       <c r="M3" t="n">
-        <v>4.216985076003029</v>
+        <v>4.201569549127663</v>
       </c>
       <c r="N3" t="n">
-        <v>29.8217564500858</v>
+        <v>29.69109926630054</v>
       </c>
       <c r="O3" t="n">
-        <v>5.460929998643619</v>
+        <v>5.448953960743341</v>
       </c>
       <c r="P3" t="n">
-        <v>402.0961337281189</v>
+        <v>402.0874794443384</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27107,28 +27233,28 @@
         <v>0.1523</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01693102841508643</v>
+        <v>0.01522161080155335</v>
       </c>
       <c r="J4" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K4" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004357797539160657</v>
+        <v>0.000355924264512586</v>
       </c>
       <c r="M4" t="n">
-        <v>4.963961685278144</v>
+        <v>4.950134912823094</v>
       </c>
       <c r="N4" t="n">
-        <v>40.16542226469626</v>
+        <v>40.00013090884516</v>
       </c>
       <c r="O4" t="n">
-        <v>6.337619605553512</v>
+        <v>6.324565669581205</v>
       </c>
       <c r="P4" t="n">
-        <v>404.2394932724009</v>
+        <v>404.2564860824947</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27185,28 +27311,28 @@
         <v>0.1123</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.007303413452335569</v>
+        <v>-0.01013363921156254</v>
       </c>
       <c r="J5" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K5" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L5" t="n">
-        <v>7.896033439391825e-05</v>
+        <v>0.0001534830034329859</v>
       </c>
       <c r="M5" t="n">
-        <v>4.920757510267918</v>
+        <v>4.912528894099419</v>
       </c>
       <c r="N5" t="n">
-        <v>41.26202227645826</v>
+        <v>41.12030342891853</v>
       </c>
       <c r="O5" t="n">
-        <v>6.423552154101207</v>
+        <v>6.412511475928797</v>
       </c>
       <c r="P5" t="n">
-        <v>409.9022030640953</v>
+        <v>409.930342252735</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27263,28 +27389,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03571505067121296</v>
+        <v>0.0335804698642069</v>
       </c>
       <c r="J6" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K6" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002073812645198569</v>
+        <v>0.001852322036105081</v>
       </c>
       <c r="M6" t="n">
-        <v>4.797384427707873</v>
+        <v>4.786357001670567</v>
       </c>
       <c r="N6" t="n">
-        <v>37.49500791717252</v>
+        <v>37.35117171463548</v>
       </c>
       <c r="O6" t="n">
-        <v>6.123316741535793</v>
+        <v>6.111560497502702</v>
       </c>
       <c r="P6" t="n">
-        <v>427.647134343675</v>
+        <v>427.6683539660957</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27341,28 +27467,28 @@
         <v>0.0931</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.009707718526889154</v>
+        <v>-0.008711462674343593</v>
       </c>
       <c r="J7" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K7" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001312150631930242</v>
+        <v>0.0001067994430294927</v>
       </c>
       <c r="M7" t="n">
-        <v>5.20883748420021</v>
+        <v>5.189879486567738</v>
       </c>
       <c r="N7" t="n">
-        <v>43.86677173289453</v>
+        <v>43.67361821778334</v>
       </c>
       <c r="O7" t="n">
-        <v>6.623199508764214</v>
+        <v>6.608601835319128</v>
       </c>
       <c r="P7" t="n">
-        <v>433.4323421697147</v>
+        <v>433.4224391733198</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27419,28 +27545,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03023477418126147</v>
+        <v>0.02969200257282854</v>
       </c>
       <c r="J8" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001361582295180352</v>
+        <v>0.001327366800736307</v>
       </c>
       <c r="M8" t="n">
-        <v>5.025029888269049</v>
+        <v>5.005019592069802</v>
       </c>
       <c r="N8" t="n">
-        <v>40.95621739815347</v>
+        <v>40.77214523537247</v>
       </c>
       <c r="O8" t="n">
-        <v>6.399704477407802</v>
+        <v>6.38530698051178</v>
       </c>
       <c r="P8" t="n">
-        <v>421.2052567009939</v>
+        <v>421.2106531156406</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27497,28 +27623,28 @@
         <v>0.1391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04231565883961118</v>
+        <v>0.04312285348687635</v>
       </c>
       <c r="J9" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K9" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003143858312535275</v>
+        <v>0.003299493416066612</v>
       </c>
       <c r="M9" t="n">
-        <v>4.668055007026168</v>
+        <v>4.650885101203451</v>
       </c>
       <c r="N9" t="n">
-        <v>34.60729771107066</v>
+        <v>34.45447411002814</v>
       </c>
       <c r="O9" t="n">
-        <v>5.882796759286407</v>
+        <v>5.869793361782691</v>
       </c>
       <c r="P9" t="n">
-        <v>418.3416035354744</v>
+        <v>418.3335690778435</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27575,28 +27701,28 @@
         <v>0.1166</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05666262312595371</v>
+        <v>0.05673496352262893</v>
       </c>
       <c r="J10" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K10" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00545355707412809</v>
+        <v>0.005526334352701556</v>
       </c>
       <c r="M10" t="n">
-        <v>4.800984256176712</v>
+        <v>4.780715099641628</v>
       </c>
       <c r="N10" t="n">
-        <v>35.68901060762892</v>
+        <v>35.52801316283892</v>
       </c>
       <c r="O10" t="n">
-        <v>5.974028005259845</v>
+        <v>5.960537992735128</v>
       </c>
       <c r="P10" t="n">
-        <v>418.4699623404398</v>
+        <v>418.4692385042009</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27653,28 +27779,28 @@
         <v>0.1266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1634397678906257</v>
+        <v>0.1642947260425313</v>
       </c>
       <c r="J11" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K11" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04158838119421759</v>
+        <v>0.04243823676455594</v>
       </c>
       <c r="M11" t="n">
-        <v>4.876817992771318</v>
+        <v>4.859046908105413</v>
       </c>
       <c r="N11" t="n">
-        <v>37.52247515270691</v>
+        <v>37.35682348443015</v>
       </c>
       <c r="O11" t="n">
-        <v>6.125559170615113</v>
+        <v>6.112022863539546</v>
       </c>
       <c r="P11" t="n">
-        <v>414.0465615203831</v>
+        <v>414.0380532536519</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27731,28 +27857,28 @@
         <v>0.0862</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1061344893586222</v>
+        <v>0.1077001028514866</v>
       </c>
       <c r="J12" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K12" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01648339418701172</v>
+        <v>0.01714019897236041</v>
       </c>
       <c r="M12" t="n">
-        <v>5.147263732190784</v>
+        <v>5.131808017308938</v>
       </c>
       <c r="N12" t="n">
-        <v>40.81058808011643</v>
+        <v>40.63979482179968</v>
       </c>
       <c r="O12" t="n">
-        <v>6.388316529424355</v>
+        <v>6.37493488765177</v>
       </c>
       <c r="P12" t="n">
-        <v>409.9538997632672</v>
+        <v>409.9382586160684</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27809,28 +27935,28 @@
         <v>0.0755</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3162660623905436</v>
+        <v>0.3162493145448204</v>
       </c>
       <c r="J13" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K13" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1019096720925724</v>
+        <v>0.1028944911692249</v>
       </c>
       <c r="M13" t="n">
-        <v>5.817311852204959</v>
+        <v>5.791496958190228</v>
       </c>
       <c r="N13" t="n">
-        <v>53.39862042603253</v>
+        <v>53.15652106607089</v>
       </c>
       <c r="O13" t="n">
-        <v>7.307435967973482</v>
+        <v>7.290851875197499</v>
       </c>
       <c r="P13" t="n">
-        <v>398.8763492225947</v>
+        <v>398.8765152015142</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27868,7 +27994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N441"/>
+  <dimension ref="A1:N443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59575,6 +59701,150 @@
         </is>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>-34.80133792031245,173.3888392535152</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>-34.801429262310904,173.3897120213197</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>-34.80142498631563,173.3905678594572</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-34.801287445642394,173.39143992136113</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-34.80107658522696,173.39227284945628</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>-34.80085098814422,173.39294795619625</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-34.80061823438421,173.39370452330618</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>-34.80027319983721,173.39447557073944</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>-34.79990083112527,173.3951711924082</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>-34.79946108914332,173.3957757666405</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-34.798983978131986,173.39635682374913</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>-34.798441014620366,173.39689651093454</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>-34.80133720007049,173.38883930321424</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>-34.80142457403471,173.38971213104114</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>-34.80142040221522,173.39056741142426</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-34.80128681761196,173.39143984438985</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>-34.80107151318843,173.3922718392863</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>-34.8008540611545,173.39294953168755</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-34.80061807835637,173.39370441364704</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-34.800270975761755,173.3944739031111</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>-34.799896208491155,173.3951668234876</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>-34.799460774008324,173.39577537572225</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-34.79898020176695,173.39635082888717</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>-34.79843965532827,173.396894062162</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
